--- a/artfynd/A 16718-2025 artfynd.xlsx
+++ b/artfynd/A 16718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127324848</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127324847</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16718-2025 artfynd.xlsx
+++ b/artfynd/A 16718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127324848</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127324847</v>
       </c>
       <c r="B3" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16718-2025 artfynd.xlsx
+++ b/artfynd/A 16718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127324848</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127324847</v>
       </c>
       <c r="B3" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16718-2025 artfynd.xlsx
+++ b/artfynd/A 16718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127324848</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127324847</v>
       </c>
       <c r="B3" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
